--- a/artfynd/A 41470-2026 artfynd.xlsx
+++ b/artfynd/A 41470-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,9 +780,243 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>137153459</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79485</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Strömnäs, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>757011</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7265628</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137153459</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137153226</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99289</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Strömnäs, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>757268</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7265379</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137153226</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41470-2026 artfynd.xlsx
+++ b/artfynd/A 41470-2026 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>137153226</v>
       </c>
       <c r="B4" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41470-2026 artfynd.xlsx
+++ b/artfynd/A 41470-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137153459</v>
       </c>
       <c r="B3" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137153226</v>
       </c>
       <c r="B4" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41470-2026 artfynd.xlsx
+++ b/artfynd/A 41470-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137153459</v>
       </c>
       <c r="B3" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137153226</v>
       </c>
       <c r="B4" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41470-2026 artfynd.xlsx
+++ b/artfynd/A 41470-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137153459</v>
       </c>
       <c r="B3" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137153226</v>
       </c>
       <c r="B4" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41470-2026 artfynd.xlsx
+++ b/artfynd/A 41470-2026 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>137153226</v>
       </c>
       <c r="B4" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41470-2026 artfynd.xlsx
+++ b/artfynd/A 41470-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137153459</v>
       </c>
       <c r="B3" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137153226</v>
       </c>
       <c r="B4" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41470-2026 artfynd.xlsx
+++ b/artfynd/A 41470-2026 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>137153226</v>
       </c>
       <c r="B4" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41470-2026 artfynd.xlsx
+++ b/artfynd/A 41470-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137153459</v>
       </c>
       <c r="B3" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137153226</v>
       </c>
       <c r="B4" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41470-2026 artfynd.xlsx
+++ b/artfynd/A 41470-2026 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>137153226</v>
       </c>
       <c r="B4" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41470-2026 artfynd.xlsx
+++ b/artfynd/A 41470-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137153459</v>
       </c>
       <c r="B3" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137153226</v>
       </c>
       <c r="B4" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41470-2026 artfynd.xlsx
+++ b/artfynd/A 41470-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137153459</v>
       </c>
       <c r="B3" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137153226</v>
       </c>
       <c r="B4" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41470-2026 artfynd.xlsx
+++ b/artfynd/A 41470-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137153459</v>
       </c>
       <c r="B3" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137153226</v>
       </c>
       <c r="B4" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41470-2026 artfynd.xlsx
+++ b/artfynd/A 41470-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137153459</v>
       </c>
       <c r="B3" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137153226</v>
       </c>
       <c r="B4" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41470-2026 artfynd.xlsx
+++ b/artfynd/A 41470-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137153459</v>
       </c>
       <c r="B3" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137153226</v>
       </c>
       <c r="B4" t="n">
-        <v>99351</v>
+        <v>99355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
